--- a/data/hex_xlsx/CTH1V.HE.xlsx
+++ b/data/hex_xlsx/CTH1V.HE.xlsx
@@ -12685,12 +12685,30 @@
       <c r="Q53" s="15">
         <v>1910.36</v>
       </c>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="18"/>
-      <c r="V53" s="18"/>
-      <c r="W53" s="18"/>
+      <c r="R53" s="15">
+        <f t="shared" ref="R53:U53" si="1">SUM(R54:R71)</f>
+        <v>2026.18</v>
+      </c>
+      <c r="S53" s="15">
+        <f t="shared" si="1"/>
+        <v>2331.89</v>
+      </c>
+      <c r="T53" s="15">
+        <f t="shared" si="1"/>
+        <v>1941.72</v>
+      </c>
+      <c r="U53" s="15">
+        <f t="shared" si="1"/>
+        <v>2016.71</v>
+      </c>
+      <c r="V53" s="18">
+        <f t="shared" ref="V53:W53" si="2">V71+V69+V66+V63+V59+V56+V55+V54</f>
+        <v>1297.45</v>
+      </c>
+      <c r="W53" s="18">
+        <f t="shared" si="2"/>
+        <v>1299.13</v>
+      </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
@@ -15450,16 +15468,46 @@
       <c r="M116" s="15">
         <v>563.12</v>
       </c>
-      <c r="N116" s="18"/>
-      <c r="O116" s="18"/>
-      <c r="P116" s="18"/>
-      <c r="Q116" s="18"/>
-      <c r="R116" s="18"/>
-      <c r="S116" s="18"/>
-      <c r="T116" s="18"/>
-      <c r="U116" s="18"/>
-      <c r="V116" s="18"/>
-      <c r="W116" s="18"/>
+      <c r="N116" s="15">
+        <f t="shared" ref="N116:W116" si="3">SUM(N118:N121)</f>
+        <v>856.32</v>
+      </c>
+      <c r="O116" s="15">
+        <f t="shared" si="3"/>
+        <v>347.91</v>
+      </c>
+      <c r="P116" s="15">
+        <f t="shared" si="3"/>
+        <v>1288.94</v>
+      </c>
+      <c r="Q116" s="15">
+        <f t="shared" si="3"/>
+        <v>97.35</v>
+      </c>
+      <c r="R116" s="15">
+        <f t="shared" si="3"/>
+        <v>377.37</v>
+      </c>
+      <c r="S116" s="15">
+        <f t="shared" si="3"/>
+        <v>478.61</v>
+      </c>
+      <c r="T116" s="15">
+        <f t="shared" si="3"/>
+        <v>1080.68</v>
+      </c>
+      <c r="U116" s="15">
+        <f t="shared" si="3"/>
+        <v>866.06</v>
+      </c>
+      <c r="V116" s="15">
+        <f t="shared" si="3"/>
+        <v>433.55</v>
+      </c>
+      <c r="W116" s="15">
+        <f t="shared" si="3"/>
+        <v>420.95</v>
+      </c>
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
